--- a/Book1_Test20250622.xlsx
+++ b/Book1_Test20250622.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pwkut\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1BB5010-17D2-4F8B-BB7F-40E179A90148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E34D0F3-7264-4728-BDEC-2BEFFD8ABCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{DC208147-DCCE-4B6C-B132-8481521DC257}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>C1</t>
   </si>
@@ -48,16 +48,28 @@
   </si>
   <si>
     <t>v2</t>
+  </si>
+  <si>
+    <t>C0</t>
+  </si>
+  <si>
+    <t>C-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -103,9 +115,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EDCE4F34-CEB3-49F4-B396-8B266AF36CE3}" name="Table1" displayName="Table1" ref="A1:B3" totalsRowShown="0">
-  <autoFilter ref="A1:B3" xr:uid="{EDCE4F34-CEB3-49F4-B396-8B266AF36CE3}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EDCE4F34-CEB3-49F4-B396-8B266AF36CE3}" name="Table1" displayName="Table1" ref="A1:D3" totalsRowShown="0">
+  <autoFilter ref="A1:D3" xr:uid="{EDCE4F34-CEB3-49F4-B396-8B266AF36CE3}"/>
+  <tableColumns count="4">
+    <tableColumn id="3" xr3:uid="{B9DDAC44-9ADA-4638-A301-5C3FE3F6F728}" name="C-1"/>
+    <tableColumn id="4" xr3:uid="{8501A374-8D74-47D4-AD2E-5720395118EB}" name="C0"/>
     <tableColumn id="1" xr3:uid="{42AC1F3F-9A89-4734-92BC-74B83C789B71}" name="C1"/>
     <tableColumn id="2" xr3:uid="{F30C90E7-138C-4BA4-8633-6FEADAE5627E}" name="C2"/>
   </tableColumns>
@@ -430,34 +444,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66CDDD7B-3A32-4A46-A8BE-5BCFFF33F112}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/Book1_Test20250622.xlsx
+++ b/Book1_Test20250622.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pwkut\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E34D0F3-7264-4728-BDEC-2BEFFD8ABCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29CD42A-AA67-469B-9450-3BEA70599DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{DC208147-DCCE-4B6C-B132-8481521DC257}"/>
   </bookViews>
@@ -38,22 +38,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
     <t>v1</t>
   </si>
   <si>
     <t>v2</t>
   </si>
   <si>
-    <t>C0</t>
+    <t>D01</t>
   </si>
   <si>
-    <t>C-1</t>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>D03</t>
+  </si>
+  <si>
+    <t>D04</t>
   </si>
 </sst>
 </file>
@@ -101,7 +101,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -118,10 +122,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EDCE4F34-CEB3-49F4-B396-8B266AF36CE3}" name="Table1" displayName="Table1" ref="A1:D3" totalsRowShown="0">
   <autoFilter ref="A1:D3" xr:uid="{EDCE4F34-CEB3-49F4-B396-8B266AF36CE3}"/>
   <tableColumns count="4">
-    <tableColumn id="3" xr3:uid="{B9DDAC44-9ADA-4638-A301-5C3FE3F6F728}" name="C-1"/>
-    <tableColumn id="4" xr3:uid="{8501A374-8D74-47D4-AD2E-5720395118EB}" name="C0"/>
-    <tableColumn id="1" xr3:uid="{42AC1F3F-9A89-4734-92BC-74B83C789B71}" name="C1"/>
-    <tableColumn id="2" xr3:uid="{F30C90E7-138C-4BA4-8633-6FEADAE5627E}" name="C2"/>
+    <tableColumn id="3" xr3:uid="{B9DDAC44-9ADA-4638-A301-5C3FE3F6F728}" name="D01" dataDxfId="0">
+      <calculatedColumnFormula>Table1[[#This Row],[D03]]&amp;
+         Table1[[#This Row],[D04]]&amp;
+    Table1[[#This Row],[D02]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{8501A374-8D74-47D4-AD2E-5720395118EB}" name="D02"/>
+    <tableColumn id="1" xr3:uid="{42AC1F3F-9A89-4734-92BC-74B83C789B71}" name="D03"/>
+    <tableColumn id="2" xr3:uid="{F30C90E7-138C-4BA4-8633-6FEADAE5627E}" name="D04"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -449,32 +457,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="str">
+        <f>Table1[[#This Row],[D03]]&amp;
+         Table1[[#This Row],[D04]]&amp;
+    Table1[[#This Row],[D02]]</f>
+        <v>v1v2</v>
+      </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f>Table1[[#This Row],[D03]]&amp;
+         Table1[[#This Row],[D04]]&amp;
+    Table1[[#This Row],[D02]]</f>
+        <v>v1v2</v>
+      </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
